--- a/backend/decade_genre_spreadsheet.xlsx
+++ b/backend/decade_genre_spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\pp\topspot_json_creator\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD689603-6CE0-4665-B0EB-9D132E9EA07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C80090DC-1E8A-4FD7-B0CC-9C8DBD491458}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{572979ED-A007-4925-8A4D-B73C469AF597}"/>
   </bookViews>
@@ -816,7 +816,7 @@
       <c r="AM5" s="3">
         <v>6</v>
       </c>
-      <c r="AN5" s="3">
+      <c r="AN5" s="4">
         <v>7</v>
       </c>
       <c r="AO5" s="3">
@@ -1158,7 +1158,7 @@
       <c r="AC8" s="3">
         <v>23</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AD8" s="4">
         <v>24</v>
       </c>
       <c r="AE8" s="3">
@@ -1539,7 +1539,7 @@
       <c r="AI11" s="3">
         <v>38</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AJ11" s="4">
         <v>39</v>
       </c>
       <c r="AK11" s="3">
@@ -1948,7 +1948,7 @@
       <c r="AI15" s="3">
         <v>8</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AJ15" s="4">
         <v>9</v>
       </c>
       <c r="AK15" s="3">
@@ -6037,7 +6037,7 @@
       <c r="I51" s="3">
         <v>36</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J51" s="4">
         <v>37</v>
       </c>
       <c r="K51" s="3">
@@ -6330,7 +6330,7 @@
       <c r="K54" s="3">
         <v>3</v>
       </c>
-      <c r="L54" s="3">
+      <c r="L54" s="4">
         <v>4</v>
       </c>
       <c r="M54" s="3">
@@ -7935,7 +7935,7 @@
       </c>
     </row>
     <row r="68" spans="1:49" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C68" s="3">
+      <c r="C68" s="4">
         <v>21</v>
       </c>
       <c r="D68" s="3">
@@ -8016,7 +8016,7 @@
       <c r="AH68" s="3">
         <v>22</v>
       </c>
-      <c r="AI68" s="3">
+      <c r="AI68" s="4">
         <v>23</v>
       </c>
       <c r="AJ68" s="3">
@@ -9178,7 +9178,7 @@
       <c r="AP78" s="3">
         <v>24</v>
       </c>
-      <c r="AQ78" s="3">
+      <c r="AQ78" s="4">
         <v>25</v>
       </c>
       <c r="AS78" s="3">
